--- a/Дело3а-78-2026Таганай/01_Иск/01.11_Комплект_Для_суда/Для суда от Виктории/Для СУДА/3. ИП МОМЗЕРОВ (масло для авто)/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/01_Иск/01.11_Комплект_Для_суда/Для суда от Виктории/Для СУДА/3. ИП МОМЗЕРОВ (масло для авто)/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46157.92565366308</v>
+        <v>46157.93088183375</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/01_Иск/01.11_Комплект_Для_суда/Для суда от Виктории/Для СУДА/3. ИП МОМЗЕРОВ (масло для авто)/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/01_Иск/01.11_Комплект_Для_суда/Для суда от Виктории/Для СУДА/3. ИП МОМЗЕРОВ (масло для авто)/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46157.93088183375</v>
+        <v>46157.93166464273</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/01_Иск/01.11_Комплект_Для_суда/Для суда от Виктории/Для СУДА/3. ИП МОМЗЕРОВ (масло для авто)/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/01_Иск/01.11_Комплект_Для_суда/Для суда от Виктории/Для СУДА/3. ИП МОМЗЕРОВ (масло для авто)/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46157.93166464273</v>
+        <v>46157.9339736189</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/01_Иск/01.11_Комплект_Для_суда/Для суда от Виктории/Для СУДА/3. ИП МОМЗЕРОВ (масло для авто)/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/01_Иск/01.11_Комплект_Для_суда/Для суда от Виктории/Для СУДА/3. ИП МОМЗЕРОВ (масло для авто)/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46157.9339736189</v>
+        <v>46157.93715019214</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/01_Иск/01.11_Комплект_Для_суда/Для суда от Виктории/Для СУДА/3. ИП МОМЗЕРОВ (масло для авто)/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/01_Иск/01.11_Комплект_Для_суда/Для суда от Виктории/Для СУДА/3. ИП МОМЗЕРОВ (масло для авто)/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46157.93715019214</v>
+        <v>46158.28213775149</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/01_Иск/01.11_Комплект_Для_суда/Для суда от Виктории/Для СУДА/3. ИП МОМЗЕРОВ (масло для авто)/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/01_Иск/01.11_Комплект_Для_суда/Для суда от Виктории/Для СУДА/3. ИП МОМЗЕРОВ (масло для авто)/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46158.28213775149</v>
+        <v>46158.29675091794</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/01_Иск/01.11_Комплект_Для_суда/Для суда от Виктории/Для СУДА/3. ИП МОМЗЕРОВ (масло для авто)/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/01_Иск/01.11_Комплект_Для_суда/Для суда от Виктории/Для СУДА/3. ИП МОМЗЕРОВ (масло для авто)/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46158.29675091794</v>
+        <v>46158.29811721011</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/01_Иск/01.11_Комплект_Для_суда/Для суда от Виктории/Для СУДА/3. ИП МОМЗЕРОВ (масло для авто)/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/01_Иск/01.11_Комплект_Для_суда/Для суда от Виктории/Для СУДА/3. ИП МОМЗЕРОВ (масло для авто)/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46158.29811721011</v>
+        <v>46158.33384630706</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/01_Иск/01.11_Комплект_Для_суда/Для суда от Виктории/Для СУДА/3. ИП МОМЗЕРОВ (масло для авто)/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/01_Иск/01.11_Комплект_Для_суда/Для суда от Виктории/Для СУДА/3. ИП МОМЗЕРОВ (масло для авто)/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46158.33384630706</v>
+        <v>46158.36853908253</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/01_Иск/01.11_Комплект_Для_суда/Для суда от Виктории/Для СУДА/3. ИП МОМЗЕРОВ (масло для авто)/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/01_Иск/01.11_Комплект_Для_суда/Для суда от Виктории/Для СУДА/3. ИП МОМЗЕРОВ (масло для авто)/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46158.36853908253</v>
+        <v>46158.37284759957</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">
